--- a/output/pdf_financials_xlsx/AURM.xlsx
+++ b/output/pdf_financials_xlsx/AURM.xlsx
@@ -2828,7 +2828,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -2856,7 +2860,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
